--- a/config/templates/epacket-standard-dmd/manifest.xlsx
+++ b/config/templates/epacket-standard-dmd/manifest.xlsx
@@ -1217,7 +1217,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
